--- a/Class Files/lookup,match,index.xlsx
+++ b/Class Files/lookup,match,index.xlsx
@@ -5,18 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shaikh zafira\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\excel sheet itvedant\Class Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44BDE1EB-4C66-4251-9F56-4E29D59BB026}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DB94684-9A13-4933-9AA0-1E627F5D4E7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="HR_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="Solutions" sheetId="2" state="hidden" r:id="rId2"/>
-    <sheet name="Practice_Tasks" sheetId="3" r:id="rId3"/>
-    <sheet name="Quick_Reference" sheetId="4" r:id="rId4"/>
+    <sheet name="Solutions" sheetId="2" state="hidden" r:id="rId1"/>
+    <sheet name="Practice_Tasks" sheetId="3" r:id="rId2"/>
+    <sheet name="Quick_Reference" sheetId="4" r:id="rId3"/>
+    <sheet name="HR_Data" sheetId="1" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1034,35 +1034,35 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1540,667 +1540,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
-    <tabColor rgb="FF2E75B6"/>
-  </sheetPr>
-  <dimension ref="A1:F40"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="26" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="46" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-    </row>
-    <row r="2" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="36">
-        <v>87950</v>
-      </c>
-      <c r="E3" s="14">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="37">
-        <v>61224</v>
-      </c>
-      <c r="E4" s="31">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="36">
-        <v>58435</v>
-      </c>
-      <c r="E5" s="38">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="37">
-        <v>67562</v>
-      </c>
-      <c r="E6" s="38">
-        <v>2</v>
-      </c>
-      <c r="F6" t="str">
-        <f>VLOOKUP(A5,$A$2:$E$33,MATCH(C2,$A$2:$E$2))</f>
-        <v>Finance</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="36">
-        <v>46348</v>
-      </c>
-      <c r="E7" s="39">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="37">
-        <v>85209</v>
-      </c>
-      <c r="E8" s="31">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="36">
-        <v>105599</v>
-      </c>
-      <c r="E9" s="17">
-        <v>1</v>
-      </c>
-      <c r="F9">
-        <f>VLOOKUP(A9,A2:E33,MATCH(D2,A2:E2,0),FALSE)</f>
-        <v>105599</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" s="37">
-        <v>116778</v>
-      </c>
-      <c r="E10" s="14">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="36">
-        <v>61144</v>
-      </c>
-      <c r="E11" s="14">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12" s="24"/>
-      <c r="E12" s="31">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="B13" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="36">
-        <v>112123</v>
-      </c>
-      <c r="E13" s="38">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14" s="37">
-        <v>84018</v>
-      </c>
-      <c r="E14" s="14">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="C15" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="D15" s="36">
-        <v>62864</v>
-      </c>
-      <c r="E15" s="38">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="C16" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="D16" s="37">
-        <v>95487</v>
-      </c>
-      <c r="E16" s="38">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="22" t="s">
-        <v>183</v>
-      </c>
-      <c r="B17" s="23" t="s">
-        <v>39</v>
-      </c>
-      <c r="C17" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="D17" s="36">
-        <v>109306</v>
-      </c>
-      <c r="E17" s="39">
-        <v>3</v>
-      </c>
-      <c r="F17">
-        <f>VLOOKUP(A17,A2:E33,MATCH(E2,A2:E2,0),FALSE)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="24" t="s">
-        <v>40</v>
-      </c>
-      <c r="B18" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="C18" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="37">
-        <v>45874</v>
-      </c>
-      <c r="E18" s="31">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="B19" s="23" t="s">
-        <v>43</v>
-      </c>
-      <c r="C19" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="D19" s="36">
-        <v>46508</v>
-      </c>
-      <c r="E19" s="14">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="B20" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="C20" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="D20" s="37">
-        <v>76468</v>
-      </c>
-      <c r="E20" s="14">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="B21" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="C21" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="D21" s="36">
-        <v>40590</v>
-      </c>
-      <c r="E21" s="39">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="B22" s="25" t="s">
-        <v>49</v>
-      </c>
-      <c r="C22" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="24"/>
-      <c r="E22" s="31">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="B23" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="C23" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="D23" s="36">
-        <v>35998</v>
-      </c>
-      <c r="E23" s="14">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="24" t="s">
-        <v>52</v>
-      </c>
-      <c r="B24" s="25" t="s">
-        <v>53</v>
-      </c>
-      <c r="C24" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="D24" s="37">
-        <v>61707</v>
-      </c>
-      <c r="E24" s="39">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="B25" s="23" t="s">
-        <v>55</v>
-      </c>
-      <c r="C25" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="D25" s="36">
-        <v>105033</v>
-      </c>
-      <c r="E25" s="17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="24" t="s">
-        <v>56</v>
-      </c>
-      <c r="B26" s="25" t="s">
-        <v>57</v>
-      </c>
-      <c r="C26" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="D26" s="37">
-        <v>95566</v>
-      </c>
-      <c r="E26" s="31">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="B27" s="23" t="s">
-        <v>59</v>
-      </c>
-      <c r="C27" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="36">
-        <v>60962</v>
-      </c>
-      <c r="E27" s="31">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="24" t="s">
-        <v>60</v>
-      </c>
-      <c r="B28" s="25" t="s">
-        <v>61</v>
-      </c>
-      <c r="C28" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D28" s="37">
-        <v>95647</v>
-      </c>
-      <c r="E28" s="17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="B29" s="23" t="s">
-        <v>63</v>
-      </c>
-      <c r="C29" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="D29" s="36">
-        <v>81861</v>
-      </c>
-      <c r="E29" s="38">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="24" t="s">
-        <v>64</v>
-      </c>
-      <c r="B30" s="25" t="s">
-        <v>65</v>
-      </c>
-      <c r="C30" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="D30" s="24"/>
-      <c r="E30" s="38">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="B31" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="D31" s="36">
-        <v>56077</v>
-      </c>
-      <c r="E31" s="14">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="B32" s="25" t="s">
-        <v>68</v>
-      </c>
-      <c r="C32" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="D32" s="37">
-        <v>113042</v>
-      </c>
-      <c r="E32" s="38">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="47" t="s">
-        <v>69</v>
-      </c>
-      <c r="B33" s="47"/>
-      <c r="C33" s="47"/>
-      <c r="D33" s="47"/>
-      <c r="E33" s="47"/>
-    </row>
-    <row r="35" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="48" t="s">
-        <v>70</v>
-      </c>
-      <c r="B35" s="48"/>
-      <c r="C35" s="48"/>
-      <c r="D35" s="48"/>
-      <c r="E35" s="48"/>
-      <c r="F35" s="48"/>
-    </row>
-    <row r="36" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="B36" s="20">
-        <v>1</v>
-      </c>
-      <c r="C36" s="20">
-        <v>2</v>
-      </c>
-      <c r="D36" s="20">
-        <v>3</v>
-      </c>
-      <c r="E36" s="20">
-        <v>4</v>
-      </c>
-      <c r="F36" s="20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="41" t="s">
-        <v>72</v>
-      </c>
-      <c r="B37" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="C37" s="42" t="s">
-        <v>74</v>
-      </c>
-      <c r="D37" s="42" t="s">
-        <v>75</v>
-      </c>
-      <c r="E37" s="42" t="s">
-        <v>76</v>
-      </c>
-      <c r="F37" s="42" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="41" t="s">
-        <v>78</v>
-      </c>
-      <c r="B38" s="43" t="s">
-        <v>79</v>
-      </c>
-      <c r="C38" s="43" t="s">
-        <v>80</v>
-      </c>
-      <c r="D38" s="43" t="s">
-        <v>81</v>
-      </c>
-      <c r="E38" s="43" t="s">
-        <v>82</v>
-      </c>
-      <c r="F38" s="43" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" t="str">
-        <f>HLOOKUP(D36,A36:F38,MATCH(A37,A36:A38,0),FALSE)</f>
-        <v>Average</v>
-      </c>
-      <c r="B40" t="str">
-        <f>HLOOKUP(C36,A36:F38,MATCH(HR_Data!A38,HR_Data!A36:A38,0),FALSE)</f>
-        <v>5%</v>
-      </c>
-      <c r="C40" t="str">
-        <f>HLOOKUP(B36,A36:F38,MATCH(A37,A36:A38,0),FALSE)</f>
-        <v>Poor</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A33:E33"/>
-    <mergeCell ref="A35:F35"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor rgb="FF375623"/>
@@ -2221,11 +1560,11 @@
       <c r="C1" s="44"/>
     </row>
     <row r="2" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="50" t="s">
         <v>85</v>
       </c>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
     </row>
     <row r="3" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="31" t="s">
@@ -2278,11 +1617,11 @@
       </c>
     </row>
     <row r="8" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="50" t="s">
+      <c r="A8" s="51" t="s">
         <v>92</v>
       </c>
-      <c r="B8" s="50"/>
-      <c r="C8" s="50"/>
+      <c r="B8" s="51"/>
+      <c r="C8" s="51"/>
     </row>
     <row r="9" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="31" t="s">
@@ -2335,11 +1674,11 @@
       </c>
     </row>
     <row r="14" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="51" t="s">
+      <c r="A14" s="52" t="s">
         <v>96</v>
       </c>
-      <c r="B14" s="51"/>
-      <c r="C14" s="51"/>
+      <c r="B14" s="52"/>
+      <c r="C14" s="52"/>
     </row>
     <row r="15" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="31" t="s">
@@ -2392,11 +1731,11 @@
       </c>
     </row>
     <row r="20" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="52" t="s">
+      <c r="A20" s="53" t="s">
         <v>100</v>
       </c>
-      <c r="B20" s="52"/>
-      <c r="C20" s="52"/>
+      <c r="B20" s="53"/>
+      <c r="C20" s="53"/>
     </row>
     <row r="21" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="31" t="s">
@@ -2449,11 +1788,11 @@
       </c>
     </row>
     <row r="26" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="53" t="s">
+      <c r="A26" s="49" t="s">
         <v>104</v>
       </c>
-      <c r="B26" s="53"/>
-      <c r="C26" s="53"/>
+      <c r="B26" s="49"/>
+      <c r="C26" s="49"/>
     </row>
     <row r="27" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="31" t="s">
@@ -2532,7 +1871,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor rgb="FFE97132"/>
@@ -2557,13 +1896,13 @@
       <c r="E1" s="44"/>
     </row>
     <row r="2" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="54" t="s">
         <v>110</v>
       </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
     </row>
     <row r="3" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -2694,7 +2033,10 @@
       <c r="D10" s="28" t="s">
         <v>120</v>
       </c>
-      <c r="E10" s="29"/>
+      <c r="E10" s="29">
+        <f>INDEX(HR_Data!A2:E32,MATCH("rohan kapoor",HR_Data!B2:B32,0),MATCH(HR_Data!D2,HR_Data!A2:E2,0))</f>
+        <v>61144</v>
+      </c>
     </row>
     <row r="11" spans="1:5" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="26">
@@ -2709,7 +2051,10 @@
       <c r="D11" s="28" t="s">
         <v>133</v>
       </c>
-      <c r="E11" s="29"/>
+      <c r="E11" s="29" t="str">
+        <f>INDEX(HR_Data!A2:E32,MATCH("kavita sharma",HR_Data!B2:B32,0),MATCH(HR_Data!C2,HR_Data!A2:E2,0))</f>
+        <v>HR</v>
+      </c>
     </row>
     <row r="12" spans="1:5" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="26">
@@ -2724,7 +2069,10 @@
       <c r="D12" s="28" t="s">
         <v>122</v>
       </c>
-      <c r="E12" s="29"/>
+      <c r="E12" s="29">
+        <f>INDEX(HR_Data!A2:E32,MATCH("suresh kumar",HR_Data!B2:B32,0),MATCH(HR_Data!E2,HR_Data!A2:E2,0))</f>
+        <v>2</v>
+      </c>
     </row>
     <row r="13" spans="1:5" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="26">
@@ -2757,7 +2105,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <tabColor rgb="FF7030A0"/>
@@ -2878,12 +2226,12 @@
       </c>
     </row>
     <row r="10" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="54" t="s">
+      <c r="A10" s="45" t="s">
         <v>163</v>
       </c>
-      <c r="B10" s="54"/>
-      <c r="C10" s="54"/>
-      <c r="D10" s="54"/>
+      <c r="B10" s="45"/>
+      <c r="C10" s="45"/>
+      <c r="D10" s="45"/>
     </row>
     <row r="11" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="20" t="s">
@@ -2975,4 +2323,674 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FF2E75B6"/>
+  </sheetPr>
+  <dimension ref="A1:I40"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="26" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="9" max="9" width="16.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="46" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+    </row>
+    <row r="2" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="36">
+        <v>87950</v>
+      </c>
+      <c r="E3" s="14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="37">
+        <v>61224</v>
+      </c>
+      <c r="E4" s="31">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="36">
+        <v>58435</v>
+      </c>
+      <c r="E5" s="38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="37">
+        <v>67562</v>
+      </c>
+      <c r="E6" s="38">
+        <v>2</v>
+      </c>
+      <c r="F6" t="str">
+        <f>VLOOKUP(A5,$A$2:$E$33,MATCH(C2,$A$2:$E$2))</f>
+        <v>Finance</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="36">
+        <v>46348</v>
+      </c>
+      <c r="E7" s="39">
+        <v>3</v>
+      </c>
+      <c r="I7" t="str">
+        <f>IFERROR(INDEX($A$2:$E$32,MATCH(C13,$C$2:$C$32,0),MATCH(B2,A$2:E$2,0)),"not found")</f>
+        <v>Aarav Shah</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="37">
+        <v>85209</v>
+      </c>
+      <c r="E8" s="31">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="36">
+        <v>105599</v>
+      </c>
+      <c r="E9" s="17">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <f>VLOOKUP(A9,A2:E33,MATCH(D2,A2:E2,0),FALSE)</f>
+        <v>105599</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="37">
+        <v>116778</v>
+      </c>
+      <c r="E10" s="14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="36">
+        <v>61144</v>
+      </c>
+      <c r="E11" s="14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="24"/>
+      <c r="E12" s="31">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="36">
+        <v>112123</v>
+      </c>
+      <c r="E13" s="38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" s="37">
+        <v>84018</v>
+      </c>
+      <c r="E14" s="14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="36">
+        <v>62864</v>
+      </c>
+      <c r="E15" s="38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="40" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="37">
+        <v>95487</v>
+      </c>
+      <c r="E16" s="38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="22" t="s">
+        <v>183</v>
+      </c>
+      <c r="B17" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="36">
+        <v>109306</v>
+      </c>
+      <c r="E17" s="39">
+        <v>3</v>
+      </c>
+      <c r="F17">
+        <f>VLOOKUP(A17,A2:E33,MATCH(E2,A2:E2,0),FALSE)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="37">
+        <v>45874</v>
+      </c>
+      <c r="E18" s="31">
+        <v>5</v>
+      </c>
+      <c r="G18">
+        <f>INDEX(HR_Data!A2:E32,MATCH("Suresh Kumar",HR_Data!B2:B32,0),MATCH(HR_Data!E2,A2:E2,0))</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" s="36">
+        <v>46508</v>
+      </c>
+      <c r="E19" s="14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="D20" s="37">
+        <v>76468</v>
+      </c>
+      <c r="E20" s="14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="B21" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="36">
+        <v>40590</v>
+      </c>
+      <c r="E21" s="39">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="B22" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="24"/>
+      <c r="E22" s="31">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="C23" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="36">
+        <v>35998</v>
+      </c>
+      <c r="E23" s="14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="B24" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="C24" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" s="37">
+        <v>61707</v>
+      </c>
+      <c r="E24" s="39">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="C25" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="D25" s="36">
+        <v>105033</v>
+      </c>
+      <c r="E25" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="C26" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="D26" s="37">
+        <v>95566</v>
+      </c>
+      <c r="E26" s="31">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="B27" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="C27" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="36">
+        <v>60962</v>
+      </c>
+      <c r="E27" s="31">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="C28" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="37">
+        <v>95647</v>
+      </c>
+      <c r="E28" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="B29" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="C29" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" s="36">
+        <v>81861</v>
+      </c>
+      <c r="E29" s="38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="B30" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="C30" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="D30" s="24"/>
+      <c r="E30" s="38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="B31" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="D31" s="36">
+        <v>56077</v>
+      </c>
+      <c r="E31" s="14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="B32" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="C32" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="D32" s="37">
+        <v>113042</v>
+      </c>
+      <c r="E32" s="38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="47" t="s">
+        <v>69</v>
+      </c>
+      <c r="B33" s="47"/>
+      <c r="C33" s="47"/>
+      <c r="D33" s="47"/>
+      <c r="E33" s="47"/>
+    </row>
+    <row r="35" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="48" t="s">
+        <v>70</v>
+      </c>
+      <c r="B35" s="48"/>
+      <c r="C35" s="48"/>
+      <c r="D35" s="48"/>
+      <c r="E35" s="48"/>
+      <c r="F35" s="48"/>
+    </row>
+    <row r="36" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="B36" s="20">
+        <v>1</v>
+      </c>
+      <c r="C36" s="20">
+        <v>2</v>
+      </c>
+      <c r="D36" s="20">
+        <v>3</v>
+      </c>
+      <c r="E36" s="20">
+        <v>4</v>
+      </c>
+      <c r="F36" s="20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="41" t="s">
+        <v>72</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>73</v>
+      </c>
+      <c r="C37" s="42" t="s">
+        <v>74</v>
+      </c>
+      <c r="D37" s="42" t="s">
+        <v>75</v>
+      </c>
+      <c r="E37" s="42" t="s">
+        <v>76</v>
+      </c>
+      <c r="F37" s="42" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="41" t="s">
+        <v>78</v>
+      </c>
+      <c r="B38" s="43" t="s">
+        <v>79</v>
+      </c>
+      <c r="C38" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="D38" s="43" t="s">
+        <v>81</v>
+      </c>
+      <c r="E38" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="F38" s="43" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" t="str">
+        <f>HLOOKUP(D36,A36:F38,MATCH(A37,A36:A38,0),FALSE)</f>
+        <v>Average</v>
+      </c>
+      <c r="B40" t="str">
+        <f>HLOOKUP(C36,A36:F38,MATCH(HR_Data!A38,HR_Data!A36:A38,0),FALSE)</f>
+        <v>5%</v>
+      </c>
+      <c r="C40" t="str">
+        <f>HLOOKUP(B36,A36:F38,MATCH(A37,A36:A38,0),FALSE)</f>
+        <v>Poor</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A35:F35"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
 </file>